--- a/04_DESIGN_TABLES/DesignTable_6401_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6401_SW2.xlsx
@@ -712,12 +712,17 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source) | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.55~1.550; HEXB@HEX=0.88~0.875; D3@BORE=0.39~0.391; D4@BORE=0.53~0.531</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1608,12 +1613,17 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source) | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.36~1.360; HEXB@HEX=0.88~0.875; D3@BORE=0.39~0.391; D4@BORE=0.41~0.406</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2125,12 +2135,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source) | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.76~1.760; HEXB@HEX=1.13~1.125; D3@BORE=0.48~0.484; D4@BORE=0.72~0.719</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2381,12 +2396,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source) | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.84~1.840; HEXB@HEX=1.25~1.250; D3@BORE=0.61~0.609; D4@BORE=0.53~0.531</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2509,7 +2529,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2519,7 +2539,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>L29=1.73 &lt; 12-8 (1.84) - non-monotonic, as-printed</t>
+          <t>L29=1.73 &lt; 12-8 (1.84) - non-monotonic, as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.73~1.730; HEXB@HEX=1.25~1.250; D3@BORE=0.61~0.609; D4@BORE=0.72~0.719</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6401_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6401_SW2.xlsx
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="C3" t="n">
         <v>0.32332</v>
@@ -804,19 +804,19 @@
         <v>0.16694</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="AA3" t="n">
         <v>0.19</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.54</v>
+        <v>0.545</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -850,7 +850,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1700 Overall Length = 1.040 (table had 1.05) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1700 Overall Length = 1.040 (table had 1.05) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.05 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.04) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.04 -&gt; Air-Way 1.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -866,7 +871,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="C4" t="n">
         <v>0.32332</v>
@@ -932,19 +937,19 @@
         <v>0.21647</v>
       </c>
       <c r="X4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Y4" t="n">
         <v>0.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.515</v>
+        <v>0.505</v>
       </c>
       <c r="AA4" t="n">
         <v>0.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.735</v>
+        <v>0.725</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -978,7 +983,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1701 Overall Length = 1.250 (table had 1.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1701 Overall Length = 1.250 (table had 1.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.23 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.25) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.25 -&gt; Air-Way 1.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -994,7 +1004,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="C5" t="n">
         <v>0.39837</v>
@@ -1060,19 +1070,19 @@
         <v>0.21647</v>
       </c>
       <c r="X5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Y5" t="n">
         <v>0.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5625</v>
+        <v>0.5675</v>
       </c>
       <c r="AA5" t="n">
         <v>0.28</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7275</v>
+        <v>0.7325</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1106,7 +1116,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1702 Overall Length = 1.290 (table had 1.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1702 Overall Length = 1.290 (table had 1.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.3 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.29) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.29 -&gt; Air-Way 1.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1122,13 +1137,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.46939</v>
+        <v>0.43301</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="n">
         <v>0.28125</v>
@@ -1188,19 +1203,19 @@
         <v>0.28378</v>
       </c>
       <c r="X6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Y6" t="n">
         <v>0.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5475</v>
+        <v>0.5675</v>
       </c>
       <c r="AA6" t="n">
         <v>0.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7125</v>
+        <v>0.7325</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1234,7 +1249,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1703 Overall Length = 1.260 (table had 1.3); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1703 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1703 Overall Length = 1.260 (table had 1.3); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1703 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.3 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; HEXB@HEX: Air-Way 0.75 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.813) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.3 | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 0.813 -&gt; Air-Way 0.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1250,7 +1270,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1316,19 +1336,19 @@
         <v>0.35064</v>
       </c>
       <c r="X7" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Y7" t="n">
         <v>0.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5925</v>
+        <v>0.5625</v>
       </c>
       <c r="AA7" t="n">
         <v>0.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9475</v>
+        <v>0.9175</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1362,7 +1382,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1704 Overall Length = 1.540 (table had 1.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1704 Overall Length = 1.540 (table had 1.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.48 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.54) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.54 -&gt; Air-Way 1.48</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1378,7 +1403,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="C8" t="n">
         <v>0.50807</v>
@@ -1444,19 +1469,19 @@
         <v>0.21647</v>
       </c>
       <c r="X8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Y8" t="n">
         <v>0.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.619</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>0.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.741</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1490,7 +1515,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1705 Overall Length = 1.360 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1705 Overall Length = 1.360 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.25 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1639,13 +1669,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="C10" t="n">
-        <v>0.61315</v>
+        <v>0.65241</v>
       </c>
       <c r="D10" t="n">
-        <v>1.062</v>
+        <v>1.13</v>
       </c>
       <c r="E10" t="n">
         <v>0.375</v>
@@ -1705,19 +1735,19 @@
         <v>0.45527</v>
       </c>
       <c r="X10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Y10" t="n">
         <v>0.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.724</v>
+        <v>0.729</v>
       </c>
       <c r="AA10" t="n">
         <v>0.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.036</v>
+        <v>1.041</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1751,12 +1781,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1708 Overall Length = 1.760 (table had 1.77); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1708 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1708 Overall Length = 1.760 (table had 1.77); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1708 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.77 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.76) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; HEXB@HEX: Air-Way 1.13 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.062) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>NPTFM radius 0.5295 is above the hex flats 0.5310 - the hex cut will flat it</t>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.76 -&gt; Air-Way 1.77 | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 1.062 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1772,7 +1802,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="C11" t="n">
         <v>0.57735</v>
@@ -1838,19 +1868,19 @@
         <v>0.28378</v>
       </c>
       <c r="X11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.699</v>
+        <v>0.719</v>
       </c>
       <c r="AA11" t="n">
         <v>0.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.761</v>
+        <v>0.781</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1884,7 +1914,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1709 Overall Length = 1.460 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1709 Overall Length = 1.460 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.5 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.46) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.46 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1900,7 +1935,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="C12" t="n">
         <v>0.57735</v>
@@ -1966,19 +2001,19 @@
         <v>0.35064</v>
       </c>
       <c r="X12" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Y12" t="n">
         <v>0.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.699</v>
+        <v>0.719</v>
       </c>
       <c r="AA12" t="n">
         <v>0.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.951</v>
+        <v>0.971</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2012,7 +2047,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1710 Overall Length = 1.650 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1710 Overall Length = 1.650 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.69 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.65) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.65 -&gt; Air-Way 1.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2161,7 +2201,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="C14" t="n">
         <v>0.7216900000000001</v>
@@ -2227,19 +2267,19 @@
         <v>0.28378</v>
       </c>
       <c r="X14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Y14" t="n">
         <v>0.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="AA14" t="n">
         <v>0.41</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2273,7 +2313,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1712 Overall Length = 1.620 (table had 1.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1712 Overall Length = 1.620 (table had 1.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.66 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.66</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2555,7 +2600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="C17" t="n">
         <v>0.79674</v>
@@ -2621,19 +2666,19 @@
         <v>0.57203</v>
       </c>
       <c r="X17" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="Y17" t="n">
         <v>0.61</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
       <c r="AA17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.233</v>
+        <v>1.188</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2667,7 +2712,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1715 Overall Length = 2.120 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1715 Overall Length = 2.120 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.03 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2683,7 +2733,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="C18" t="n">
         <v>0.86603</v>
@@ -2749,19 +2799,19 @@
         <v>0.45527</v>
       </c>
       <c r="X18" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Y18" t="n">
         <v>0.84</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.902</v>
+        <v>0.857</v>
       </c>
       <c r="AA18" t="n">
         <v>0.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.058</v>
+        <v>1.013</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2795,7 +2845,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1716 Overall Length = 1.960 (table had 1.87) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1716 Overall Length = 1.960 (table had 1.87) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.87 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.96) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.96 -&gt; Air-Way 1.87</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -2811,7 +2866,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="C19" t="n">
         <v>0.86603</v>
@@ -2877,19 +2932,19 @@
         <v>0.57203</v>
       </c>
       <c r="X19" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Y19" t="n">
         <v>0.84</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.887</v>
+        <v>0.857</v>
       </c>
       <c r="AA19" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.233</v>
+        <v>1.203</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2923,7 +2978,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1717 Overall Length = 2.120 (table had 2.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1717 Overall Length = 2.120 (table had 2.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.06 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.06</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3205,7 +3265,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="C22" t="n">
         <v>1.08542</v>
@@ -3271,19 +3331,19 @@
         <v>0.74378</v>
       </c>
       <c r="X22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Y22" t="n">
         <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.892</v>
+        <v>0.897</v>
       </c>
       <c r="AA22" t="n">
         <v>1.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.268</v>
+        <v>1.273</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3317,7 +3377,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1720 Overall Length = 2.160 (table had 2.17) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1720 Overall Length = 2.160 (table had 2.17) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.17 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.16 -&gt; Air-Way 2.17</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3466,7 +3531,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="C24" t="n">
         <v>1.22976</v>
@@ -3532,19 +3597,19 @@
         <v>0.86326</v>
       </c>
       <c r="X24" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="Y24" t="n">
         <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="AA24" t="n">
         <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.343</v>
+        <v>1.338</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3578,7 +3643,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1722 Overall Length = 2.280 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1722 Overall Length = 2.280 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.27 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.28 -&gt; Air-Way 2.27</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -3594,7 +3664,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="C25" t="n">
         <v>1.58771</v>
@@ -3660,19 +3730,19 @@
         <v>1.09973</v>
       </c>
       <c r="X25" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="Y25" t="n">
         <v>1.78</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.022</v>
+        <v>1.017</v>
       </c>
       <c r="AA25" t="n">
         <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.458</v>
+        <v>1.453</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3706,12 +3776,12 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1723 Overall Length = 2.480 (table had 2.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1723 Overall Length = 2.480 (table had 2.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.47 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6401 review table (ORD-5700 groove, measured thread length; no tip chamfer modelled); NPTF male per ASME B1.20.3 + measured end length; bore step at hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)</t>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)| 2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.48 -&gt; Air-Way 2.47</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
